--- a/docs/template/monthly-finance-report.xlsx
+++ b/docs/template/monthly-finance-report.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/restupriyono/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3C9CB4-3C22-C442-A339-7C888ED0FBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3F687F-1B79-D148-BE51-C545F4F94011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16840" xr2:uid="{A9BFB524-1C3E-0D4B-A649-EFD2120362A4}"/>
   </bookViews>
@@ -35,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>NAMA KOPERASI</t>
   </si>
@@ -155,6 +150,9 @@
   </si>
   <si>
     <t>AKUMULASI CAD</t>
+  </si>
+  <si>
+    <t>1+2+3</t>
   </si>
 </sst>
 </file>
@@ -296,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -307,24 +305,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -340,6 +330,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -654,13 +661,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7714CBC3-9DF7-A74A-A37E-6CB4AEF36C83}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16" width="13.6640625" customWidth="1"/>
+    <col min="1" max="14" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -677,10 +684,8 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" ht="19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -695,747 +700,668 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="12" t="s">
+    </row>
+    <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="H4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="J4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="K4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="L4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="M4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="N4" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="16"/>
-      <c r="B5" s="5">
+    <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="5">
+      <c r="D5" s="4">
         <v>2</v>
       </c>
-      <c r="D5" s="5">
+      <c r="E5" s="4">
         <v>3</v>
       </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
-        <v>2</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B8" s="14"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="16">
         <f t="shared" ref="B19" si="0">SUM(B6:B18)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="16">
         <f t="shared" ref="C19" si="1">SUM(C6:C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="16">
         <f t="shared" ref="D19" si="2">SUM(D6:D18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="16">
         <f t="shared" ref="E19" si="3">SUM(E6:E18)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="7">
-        <f t="shared" ref="F19" si="4">SUM(F6:F18)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="7">
-        <f t="shared" ref="G19" si="5">SUM(G6:G18)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
-        <f t="shared" ref="E19:P19" si="6">SUM(H6:H18)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="F19" s="16">
+        <f t="shared" ref="F19:N19" si="4">SUM(F6:F18)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
+      <c r="B32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="11">
-        <f t="shared" ref="B34" si="7">SUM(B22:B33)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="11">
-        <f t="shared" ref="C34" si="8">SUM(C22:C33)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="11">
-        <f t="shared" ref="D34" si="9">SUM(D22:D33)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="11">
-        <f t="shared" ref="E34" si="10">SUM(E22:E33)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="11">
-        <f t="shared" ref="F34" si="11">SUM(F22:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="11">
-        <f t="shared" ref="G34:P34" si="12">SUM(G22:G33)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N34" s="11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="11">
-        <f t="shared" ref="O34" si="13">SUM(O22:O33)</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="11">
-        <f t="shared" ref="P34" si="14">SUM(P22:P33)</f>
+      <c r="B34" s="19">
+        <f t="shared" ref="B34" si="5">SUM(B22:B33)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="19">
+        <f t="shared" ref="C34" si="6">SUM(C22:C33)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="19">
+        <f t="shared" ref="D34" si="7">SUM(D22:D33)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="19">
+        <f t="shared" ref="E34:L34" si="8">SUM(E22:E33)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="19">
+        <f t="shared" ref="M34" si="9">SUM(M22:M33)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="19">
+        <f t="shared" ref="N34" si="10">SUM(N22:N33)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
